--- a/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_ITA_grids_kan/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_ITA_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9FF1CCD6-5810-46B5-80BB-516106734B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C419405B-186F-4E3C-AA7B-89A52754EFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -799,13 +799,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S01aH02,S03aH02,S02aH02</t>
+    <t>S03aH02,S01aH02,S02aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH03,S01aH03,S02aH01,S03aH01,S03aH03,S01aH01</t>
+    <t>S02aH03,S03aH01,S03aH03,S01aH03,S02aH01,S01aH01</t>
   </si>
   <si>
     <t>com_pkflx</t>
@@ -943,10 +943,10 @@
     <t>S07aH06</t>
   </si>
   <si>
-    <t>S03aH02,S07aH05,S02aH02,S01aH05,S06aH05,S02aH04,S02aH05,S04aH02,S04aH05,S01aH04,S07aH02,S02aH03,S07aH03,S03aH05,S05aH05,S06aH04,S04aH03,S07aH04,S03aH03,S05aH04,S06aH02,S06aH03,S03aH04,S01aH03,S05aH02,S05aH03,S01aH02,S04aH04</t>
+    <t>S01aH05,S06aH05,S03aH03,S02aH02,S03aH05,S05aH05,S06aH04,S04aH02,S04aH05,S01aH04,S07aH02,S03aH02,S07aH05,S03aH04,S01aH02,S04aH04,S01aH03,S05aH02,S05aH03,S02aH04,S02aH05,S05aH04,S06aH02,S06aH03,S02aH03,S07aH03,S04aH03,S07aH04</t>
   </si>
   <si>
-    <t>S03aH01,S06aH01,S02aH06,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06,S06aH06,S01aH06,S07aH01,S05aH01,S07aH06,S03aH06</t>
+    <t>S06aH06,S03aH01,S06aH01,S05aH01,S07aH06,S03aH06,S02aH06,S01aH06,S07aH01,S01aH01,S04aH01,S04aH06,S02aH01,S05aH06</t>
   </si>
   <si>
     <t>AllS</t>
@@ -1012,10 +1012,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaP,SaD,FaP,SaP,RaP,WaD,FaD,RaD</t>
+    <t>FaD,RaD,WaD,SaD,RaP,WaP,FaP,SaP</t>
   </si>
   <si>
-    <t>RaN,WaP,FaP,SaP,SaN,WaN,FaN,RaP</t>
+    <t>WaP,RaP,FaN,FaP,SaP,SaN,WaN,RaN</t>
   </si>
 </sst>
 </file>
@@ -24676,7 +24676,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFE3B6A-9F92-42C9-8A96-89605A9C3355}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE599A3-340B-4801-ADAD-B0FBCD5F529C}">
   <dimension ref="A9:AN226"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25681,7 +25681,7 @@
         <v>159</v>
       </c>
       <c r="AM21">
-        <v>0.28716666666666663</v>
+        <v>0.28716666666666668</v>
       </c>
       <c r="AN21" t="s">
         <v>245</v>
@@ -26194,7 +26194,7 @@
         <v>159</v>
       </c>
       <c r="AM30">
-        <v>0.25663333333333332</v>
+        <v>0.25663333333333338</v>
       </c>
       <c r="AN30" t="s">
         <v>245</v>
@@ -26494,7 +26494,7 @@
         <v>159</v>
       </c>
       <c r="AM36">
-        <v>0.25435555555555556</v>
+        <v>0.2543555555555555</v>
       </c>
       <c r="AN36" t="s">
         <v>245</v>
@@ -26644,7 +26644,7 @@
         <v>159</v>
       </c>
       <c r="AM39">
-        <v>0.24632222222222222</v>
+        <v>0.24632222222222216</v>
       </c>
       <c r="AN39" t="s">
         <v>245</v>
@@ -27094,7 +27094,7 @@
         <v>159</v>
       </c>
       <c r="AM48">
-        <v>0.25573333333333337</v>
+        <v>0.25573333333333331</v>
       </c>
       <c r="AN48" t="s">
         <v>245</v>
@@ -27394,7 +27394,7 @@
         <v>159</v>
       </c>
       <c r="AM54">
-        <v>0.24186666666666667</v>
+        <v>0.24186666666666662</v>
       </c>
       <c r="AN54" t="s">
         <v>245</v>
@@ -27994,7 +27994,7 @@
         <v>159</v>
       </c>
       <c r="AM66">
-        <v>0.24700000000000003</v>
+        <v>0.247</v>
       </c>
       <c r="AN66" t="s">
         <v>245</v>
@@ -28594,7 +28594,7 @@
         <v>159</v>
       </c>
       <c r="AM78">
-        <v>0.25235555555555556</v>
+        <v>0.25235555555555561</v>
       </c>
       <c r="AN78" t="s">
         <v>245</v>
@@ -29044,7 +29044,7 @@
         <v>159</v>
       </c>
       <c r="AM87">
-        <v>0.25183333333333335</v>
+        <v>0.2518333333333333</v>
       </c>
       <c r="AN87" t="s">
         <v>245</v>
@@ -29494,7 +29494,7 @@
         <v>159</v>
       </c>
       <c r="AM96">
-        <v>0.24277777777777773</v>
+        <v>0.24277777777777784</v>
       </c>
       <c r="AN96" t="s">
         <v>245</v>
@@ -33378,7 +33378,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{357FBC41-7649-4AFB-B3AF-7139D70745D0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A3A635-C7F3-4A4C-901F-9C35267E200A}">
   <dimension ref="A9:AN1018"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -34295,7 +34295,7 @@
         <v>159</v>
       </c>
       <c r="AM19">
-        <v>0.26922212123117611</v>
+        <v>0.26922212123117606</v>
       </c>
       <c r="AN19" t="s">
         <v>245</v>
@@ -38705,7 +38705,7 @@
         <v>159</v>
       </c>
       <c r="AM82">
-        <v>0.25187500000000002</v>
+        <v>0.25187499999999996</v>
       </c>
       <c r="AN82" t="s">
         <v>245</v>
@@ -42313,7 +42313,7 @@
         <v>159</v>
       </c>
       <c r="AM152">
-        <v>0.26854999999999996</v>
+        <v>0.26855000000000001</v>
       </c>
       <c r="AN152" t="s">
         <v>245</v>
@@ -43713,7 +43713,7 @@
         <v>159</v>
       </c>
       <c r="AM180">
-        <v>0.24722499999999997</v>
+        <v>0.247225</v>
       </c>
       <c r="AN180" t="s">
         <v>245</v>
@@ -44413,7 +44413,7 @@
         <v>159</v>
       </c>
       <c r="AM194">
-        <v>0.24832499999999999</v>
+        <v>0.24832500000000002</v>
       </c>
       <c r="AN194" t="s">
         <v>245</v>
@@ -45113,7 +45113,7 @@
         <v>159</v>
       </c>
       <c r="AM208">
-        <v>0.25054999999999999</v>
+        <v>0.25055000000000005</v>
       </c>
       <c r="AN208" t="s">
         <v>245</v>
@@ -70925,7 +70925,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85B667BE-A854-4615-9CAF-9A94350BE0D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{262F5ADA-9771-4569-BAD7-664A61E69739}">
   <dimension ref="A9:AN39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -71363,7 +71363,7 @@
         <v>289</v>
       </c>
       <c r="AM15">
-        <v>0.199875</v>
+        <v>0.19987500000000002</v>
       </c>
       <c r="AN15" t="s">
         <v>245</v>
@@ -71463,7 +71463,7 @@
         <v>289</v>
       </c>
       <c r="AM17">
-        <v>0.236175</v>
+        <v>0.23617500000000002</v>
       </c>
       <c r="AN17" t="s">
         <v>245</v>
@@ -71513,7 +71513,7 @@
         <v>289</v>
       </c>
       <c r="AM18">
-        <v>0.22822499999999998</v>
+        <v>0.22822500000000001</v>
       </c>
       <c r="AN18" t="s">
         <v>245</v>
@@ -71563,7 +71563,7 @@
         <v>289</v>
       </c>
       <c r="AM19">
-        <v>0.23554166666666665</v>
+        <v>0.23554166666666668</v>
       </c>
       <c r="AN19" t="s">
         <v>245</v>
@@ -71613,7 +71613,7 @@
         <v>289</v>
       </c>
       <c r="AM20">
-        <v>0.23180000000000001</v>
+        <v>0.23179999999999998</v>
       </c>
       <c r="AN20" t="s">
         <v>245</v>
@@ -71663,7 +71663,7 @@
         <v>289</v>
       </c>
       <c r="AM21">
-        <v>0.23264166666666664</v>
+        <v>0.23264166666666672</v>
       </c>
       <c r="AN21" t="s">
         <v>245</v>
@@ -71713,7 +71713,7 @@
         <v>289</v>
       </c>
       <c r="AM22">
-        <v>0.22911666666666666</v>
+        <v>0.22911666666666664</v>
       </c>
       <c r="AN22" t="s">
         <v>245</v>
@@ -71813,7 +71813,7 @@
         <v>289</v>
       </c>
       <c r="AM24">
-        <v>0.23117500000000002</v>
+        <v>0.23117499999999999</v>
       </c>
       <c r="AN24" t="s">
         <v>245</v>
@@ -71863,7 +71863,7 @@
         <v>289</v>
       </c>
       <c r="AM25">
-        <v>0.22721666666666665</v>
+        <v>0.22721666666666671</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -71913,7 +71913,7 @@
         <v>289</v>
       </c>
       <c r="AM26">
-        <v>0.23520833333333332</v>
+        <v>0.23520833333333335</v>
       </c>
       <c r="AN26" t="s">
         <v>245</v>
@@ -71963,7 +71963,7 @@
         <v>289</v>
       </c>
       <c r="AM27">
-        <v>0.23155000000000001</v>
+        <v>0.23155000000000003</v>
       </c>
       <c r="AN27" t="s">
         <v>245</v>
@@ -72013,7 +72013,7 @@
         <v>289</v>
       </c>
       <c r="AM28">
-        <v>0.2262666666666667</v>
+        <v>0.22626666666666664</v>
       </c>
       <c r="AN28" t="s">
         <v>245</v>
@@ -72063,7 +72063,7 @@
         <v>289</v>
       </c>
       <c r="AM29">
-        <v>0.22933333333333336</v>
+        <v>0.22933333333333331</v>
       </c>
       <c r="AN29" t="s">
         <v>245</v>
@@ -72089,7 +72089,7 @@
         <v>289</v>
       </c>
       <c r="AM30">
-        <v>0.22550833333333331</v>
+        <v>0.22550833333333334</v>
       </c>
       <c r="AN30" t="s">
         <v>245</v>
@@ -72115,7 +72115,7 @@
         <v>289</v>
       </c>
       <c r="AM31">
-        <v>0.23632499999999998</v>
+        <v>0.23632500000000001</v>
       </c>
       <c r="AN31" t="s">
         <v>245</v>
@@ -72167,7 +72167,7 @@
         <v>289</v>
       </c>
       <c r="AM33">
-        <v>0.23614999999999997</v>
+        <v>0.23615</v>
       </c>
       <c r="AN33" t="s">
         <v>245</v>
@@ -72207,7 +72207,7 @@
         <v>289</v>
       </c>
       <c r="AM35">
-        <v>0.22216666666666671</v>
+        <v>0.22216666666666665</v>
       </c>
       <c r="AN35" t="s">
         <v>245</v>
@@ -72263,7 +72263,7 @@
         <v>289</v>
       </c>
       <c r="AM39">
-        <v>0.22639999999999996</v>
+        <v>0.22640000000000002</v>
       </c>
       <c r="AN39" t="s">
         <v>245</v>
@@ -72275,7 +72275,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68B44796-08DD-41CB-87B4-47ECE6669847}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B626FA06-7B2A-42D2-AF8D-00158F6910E5}">
   <dimension ref="A9:AN298"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -72925,7 +72925,7 @@
         <v>294</v>
       </c>
       <c r="AM16">
-        <v>0.23614596572529034</v>
+        <v>0.23614596572529031</v>
       </c>
       <c r="AN16" t="s">
         <v>245</v>
@@ -73582,7 +73582,7 @@
         <v>295</v>
       </c>
       <c r="AM25">
-        <v>0.36296666666666666</v>
+        <v>0.3629666666666666</v>
       </c>
       <c r="AN25" t="s">
         <v>245</v>
@@ -74213,7 +74213,7 @@
         <v>294</v>
       </c>
       <c r="AM36">
-        <v>0.23303333333333331</v>
+        <v>0.23303333333333334</v>
       </c>
       <c r="AN36" t="s">
         <v>245</v>
@@ -74613,7 +74613,7 @@
         <v>294</v>
       </c>
       <c r="AM44">
-        <v>0.23766666666666666</v>
+        <v>0.23766666666666669</v>
       </c>
       <c r="AN44" t="s">
         <v>245</v>
@@ -74863,7 +74863,7 @@
         <v>295</v>
       </c>
       <c r="AM49">
-        <v>0.31953333333333334</v>
+        <v>0.31953333333333339</v>
       </c>
       <c r="AN49" t="s">
         <v>245</v>
@@ -75263,7 +75263,7 @@
         <v>295</v>
       </c>
       <c r="AM57">
-        <v>0.29526666666666662</v>
+        <v>0.29526666666666668</v>
       </c>
       <c r="AN57" t="s">
         <v>245</v>
@@ -75413,7 +75413,7 @@
         <v>294</v>
       </c>
       <c r="AM60">
-        <v>0.22609999999999997</v>
+        <v>0.2261</v>
       </c>
       <c r="AN60" t="s">
         <v>245</v>
@@ -75663,7 +75663,7 @@
         <v>295</v>
       </c>
       <c r="AM65">
-        <v>0.31743333333333335</v>
+        <v>0.31743333333333329</v>
       </c>
       <c r="AN65" t="s">
         <v>245</v>
@@ -76013,7 +76013,7 @@
         <v>294</v>
       </c>
       <c r="AM72">
-        <v>0.24016666666666664</v>
+        <v>0.24016666666666667</v>
       </c>
       <c r="AN72" t="s">
         <v>245</v>
@@ -76063,7 +76063,7 @@
         <v>295</v>
       </c>
       <c r="AM73">
-        <v>0.30233333333333334</v>
+        <v>0.30233333333333329</v>
       </c>
       <c r="AN73" t="s">
         <v>245</v>
@@ -76663,7 +76663,7 @@
         <v>295</v>
       </c>
       <c r="AM85">
-        <v>0.30069999999999997</v>
+        <v>0.30070000000000002</v>
       </c>
       <c r="AN85" t="s">
         <v>245</v>
@@ -77063,7 +77063,7 @@
         <v>295</v>
       </c>
       <c r="AM93">
-        <v>0.32769999999999994</v>
+        <v>0.32770000000000005</v>
       </c>
       <c r="AN93" t="s">
         <v>245</v>
@@ -78213,7 +78213,7 @@
         <v>294</v>
       </c>
       <c r="AM116">
-        <v>0.21740000000000004</v>
+        <v>0.21740000000000001</v>
       </c>
       <c r="AN116" t="s">
         <v>245</v>
@@ -78263,7 +78263,7 @@
         <v>295</v>
       </c>
       <c r="AM117">
-        <v>0.30860000000000004</v>
+        <v>0.30859999999999999</v>
       </c>
       <c r="AN117" t="s">
         <v>245</v>
@@ -78413,7 +78413,7 @@
         <v>294</v>
       </c>
       <c r="AM120">
-        <v>0.22660000000000002</v>
+        <v>0.2266</v>
       </c>
       <c r="AN120" t="s">
         <v>245</v>
@@ -78463,7 +78463,7 @@
         <v>295</v>
       </c>
       <c r="AM121">
-        <v>0.30459999999999998</v>
+        <v>0.30460000000000004</v>
       </c>
       <c r="AN121" t="s">
         <v>245</v>
@@ -78613,7 +78613,7 @@
         <v>294</v>
       </c>
       <c r="AM124">
-        <v>0.22013333333333332</v>
+        <v>0.22013333333333338</v>
       </c>
       <c r="AN124" t="s">
         <v>245</v>
